--- a/data/601127_赛力斯_财务数据.xlsx
+++ b/data/601127_赛力斯_财务数据.xlsx
@@ -11137,7 +11137,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>归属于少数股东的综合收益总额</t>
+          <t>minority_common_profit_total</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
@@ -18527,7 +18527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC11"/>
+  <dimension ref="A1:AA11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -18557,8 +18557,6 @@
     <col width="16" customWidth="1" min="25" max="25"/>
     <col width="16" customWidth="1" min="26" max="26"/>
     <col width="16" customWidth="1" min="27" max="27"/>
-    <col width="16" customWidth="1" min="28" max="28"/>
-    <col width="16" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18605,22 +18603,22 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>财务费用率(%)</t>
+          <t>资产负债率(%)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>资产负债率(%)</t>
+          <t>流动比率</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>流动比率</t>
+          <t>速动比率</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>速动比率</t>
+          <t>产权比率(%)</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
@@ -18630,75 +18628,65 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>应收账款周转天数(天)</t>
+          <t>存货周转率(次)</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>存货周转率(次)</t>
+          <t>总资产周转率(次)</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>存货周转天数(天)</t>
+          <t>流动资产周转率(次)</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>总资产周转率(次)</t>
+          <t>固定资产周转率(次)</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>流动资产周转率(次)</t>
+          <t>营收同比(%)</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>固定资产周转率(次)</t>
+          <t>净利润同比(%)</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>营收同比(%)</t>
+          <t>总资产增长率(%)</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>净利润同比(%)</t>
+          <t>经营现金流/净利润</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>总资产增长率(%)</t>
+          <t>自由现金流(元)</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>经营现金流/净利润</t>
+          <t>现金收入比</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>自由现金流(元)</t>
+          <t>现金流组合</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>现金收入比</t>
+          <t>Altman Z-score</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>现金流组合</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Altman Z-score</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Z-score判定</t>
         </is>
@@ -18732,58 +18720,52 @@
         <v>5.296608641349956</v>
       </c>
       <c r="I2" s="4" t="inlineStr"/>
-      <c r="J2" s="6" t="n">
-        <v>0.1928282596785079</v>
-      </c>
-      <c r="K2" s="3" t="n">
+      <c r="J2" s="3" t="n">
         <v>76.94091550715871</v>
       </c>
+      <c r="K2" s="6" t="n">
+        <v>0.8972404545133743</v>
+      </c>
       <c r="L2" s="6" t="n">
-        <v>0.8972404545133743</v>
-      </c>
-      <c r="M2" s="6" t="n">
         <v>0.8202413720093161</v>
+      </c>
+      <c r="M2" s="3" t="n">
+        <v>333.6685614341932</v>
       </c>
       <c r="N2" s="3" t="n">
         <v>2.173772767571486</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>165.6106863470315</v>
-      </c>
-      <c r="P2" s="3" t="n">
         <v>14.24401988285976</v>
       </c>
+      <c r="P2" s="6" t="n">
+        <v>0.8163154540048396</v>
+      </c>
       <c r="Q2" s="3" t="n">
-        <v>25.27376421547953</v>
-      </c>
-      <c r="R2" s="6" t="n">
-        <v>0.8163154540048396</v>
-      </c>
-      <c r="S2" s="3" t="n">
         <v>1.273690973463384</v>
       </c>
+      <c r="R2" s="4" t="inlineStr"/>
+      <c r="S2" s="4" t="inlineStr"/>
       <c r="T2" s="4" t="inlineStr"/>
       <c r="U2" s="4" t="inlineStr"/>
-      <c r="V2" s="4" t="inlineStr"/>
-      <c r="W2" s="4" t="inlineStr"/>
-      <c r="X2" s="3" t="n">
+      <c r="V2" s="3" t="n">
         <v>1.804454173539292</v>
       </c>
-      <c r="Y2" s="3" t="n">
+      <c r="W2" s="3" t="n">
         <v>503000000</v>
       </c>
-      <c r="Z2" s="6" t="n">
+      <c r="X2" s="6" t="n">
         <v>0.8116754115612219</v>
       </c>
+      <c r="Y2" s="4" t="inlineStr">
+        <is>
+          <t>+/−/+</t>
+        </is>
+      </c>
+      <c r="Z2" s="3" t="n">
+        <v>1.175438147494606</v>
+      </c>
       <c r="AA2" s="4" t="inlineStr">
-        <is>
-          <t>+/−/+</t>
-        </is>
-      </c>
-      <c r="AB2" s="3" t="n">
-        <v>1.175438147494606</v>
-      </c>
-      <c r="AC2" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -18819,64 +18801,58 @@
       <c r="I3" s="3" t="n">
         <v>2.13284102224287</v>
       </c>
-      <c r="J3" s="6" t="n">
-        <v>0.1377402416277752</v>
-      </c>
-      <c r="K3" s="3" t="n">
+      <c r="J3" s="3" t="n">
         <v>75.44066795985493</v>
       </c>
+      <c r="K3" s="6" t="n">
+        <v>0.9968669498015735</v>
+      </c>
       <c r="L3" s="6" t="n">
-        <v>0.9968669498015735</v>
-      </c>
-      <c r="M3" s="6" t="n">
         <v>0.9037109239016918</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>307.1771978021978</v>
       </c>
       <c r="N3" s="3" t="n">
         <v>3.135410465537845</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>114.8175028299671</v>
+        <v>17.01502574662824</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>17.01502574662824</v>
+        <v>1.00729110960597</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>21.15776992411186</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>1.00729110960597</v>
-      </c>
+        <v>1.62285996904813</v>
+      </c>
+      <c r="R3" s="4" t="inlineStr"/>
       <c r="S3" s="3" t="n">
-        <v>1.62285996904813</v>
-      </c>
-      <c r="T3" s="4" t="inlineStr"/>
+        <v>35.45687324120385</v>
+      </c>
+      <c r="T3" s="3" t="n">
+        <v>73.41488050556718</v>
+      </c>
       <c r="U3" s="3" t="n">
-        <v>35.45687324120385</v>
-      </c>
-      <c r="V3" s="3" t="n">
-        <v>73.41488050556718</v>
+        <v>19.55031256301674</v>
+      </c>
+      <c r="V3" s="6" t="n">
+        <v>0.9052531334425789</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>19.55031256301674</v>
+        <v>-596999999.9999999</v>
       </c>
       <c r="X3" s="6" t="n">
-        <v>0.9052531334425789</v>
-      </c>
-      <c r="Y3" s="3" t="n">
-        <v>-596999999.9999999</v>
-      </c>
-      <c r="Z3" s="6" t="n">
         <v>0.8838428314478919</v>
       </c>
+      <c r="Y3" s="4" t="inlineStr">
+        <is>
+          <t>+/−/+</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="n">
+        <v>1.472587496013353</v>
+      </c>
       <c r="AA3" s="4" t="inlineStr">
-        <is>
-          <t>+/−/+</t>
-        </is>
-      </c>
-      <c r="AB3" s="3" t="n">
-        <v>1.472587496013353</v>
-      </c>
-      <c r="AC3" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -18912,64 +18888,58 @@
       <c r="I4" s="3" t="n">
         <v>2.386942497714987</v>
       </c>
-      <c r="J4" s="6" t="n">
-        <v>0.5954684860925293</v>
-      </c>
-      <c r="K4" s="3" t="n">
+      <c r="J4" s="3" t="n">
         <v>72.99549800945046</v>
       </c>
+      <c r="K4" s="6" t="n">
+        <v>0.8598784393176917</v>
+      </c>
       <c r="L4" s="6" t="n">
-        <v>0.8598784393176917</v>
-      </c>
-      <c r="M4" s="6" t="n">
         <v>0.7440036598915104</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>270.3086249655553</v>
       </c>
       <c r="N4" s="3" t="n">
         <v>3.294503659477496</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>109.2729094303375</v>
-      </c>
-      <c r="P4" s="3" t="n">
         <v>12.5500520979235</v>
       </c>
+      <c r="P4" s="6" t="n">
+        <v>0.8001337483742168</v>
+      </c>
       <c r="Q4" s="3" t="n">
-        <v>28.6851398855599</v>
-      </c>
-      <c r="R4" s="6" t="n">
-        <v>0.8001337483742168</v>
-      </c>
+        <v>1.473323620163785</v>
+      </c>
+      <c r="R4" s="4" t="inlineStr"/>
       <c r="S4" s="3" t="n">
-        <v>1.473323620163785</v>
-      </c>
-      <c r="T4" s="4" t="inlineStr"/>
+        <v>-7.723164553479601</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>-54.88088344626135</v>
+      </c>
       <c r="U4" s="3" t="n">
-        <v>-7.723164553479601</v>
+        <v>13.33811250737961</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>-54.88088344626135</v>
+        <v>2.247850708670221</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>13.33811250737961</v>
-      </c>
-      <c r="X4" s="3" t="n">
-        <v>2.247850708670221</v>
-      </c>
-      <c r="Y4" s="3" t="n">
         <v>-1467000000</v>
       </c>
-      <c r="Z4" s="6" t="n">
+      <c r="X4" s="6" t="n">
         <v>0.8618175303588153</v>
       </c>
+      <c r="Y4" s="4" t="inlineStr">
+        <is>
+          <t>+/−/+</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="n">
+        <v>1.117217969442017</v>
+      </c>
       <c r="AA4" s="4" t="inlineStr">
-        <is>
-          <t>+/−/+</t>
-        </is>
-      </c>
-      <c r="AB4" s="3" t="n">
-        <v>1.117217969442017</v>
-      </c>
-      <c r="AC4" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -19006,63 +18976,57 @@
         <v>3.592543289324201</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>1.274178795630854</v>
-      </c>
-      <c r="K5" s="3" t="n">
         <v>73.76315349924836</v>
       </c>
+      <c r="K5" s="6" t="n">
+        <v>0.8191932413136601</v>
+      </c>
       <c r="L5" s="6" t="n">
-        <v>0.8191932413136601</v>
-      </c>
-      <c r="M5" s="6" t="n">
         <v>0.6853879105188005</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>281.1433664374841</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>4.939255019869245</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>72.88548547338019</v>
-      </c>
-      <c r="P5" s="3" t="n">
         <v>9.370754937578321</v>
       </c>
+      <c r="P5" s="6" t="n">
+        <v>0.638316031047666</v>
+      </c>
       <c r="Q5" s="3" t="n">
-        <v>38.4173956525465</v>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v>0.638316031047666</v>
-      </c>
+        <v>1.34680273177895</v>
+      </c>
+      <c r="R5" s="4" t="inlineStr"/>
       <c r="S5" s="3" t="n">
-        <v>1.34680273177895</v>
-      </c>
-      <c r="T5" s="4" t="inlineStr"/>
+        <v>-10.41403472507309</v>
+      </c>
+      <c r="T5" s="3" t="n">
+        <v>-82.81471395233515</v>
+      </c>
       <c r="U5" s="3" t="n">
-        <v>-10.41403472507309</v>
+        <v>11.37775793429327</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>-82.81471395233515</v>
+        <v>3.88772564507483</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>11.37775793429327</v>
-      </c>
-      <c r="X5" s="3" t="n">
-        <v>3.88772564507483</v>
-      </c>
-      <c r="Y5" s="3" t="n">
         <v>-2370000000</v>
       </c>
+      <c r="X5" s="6" t="n">
+        <v>0.9418153057212033</v>
+      </c>
+      <c r="Y5" s="4" t="inlineStr">
+        <is>
+          <t>+/−/+</t>
+        </is>
+      </c>
       <c r="Z5" s="6" t="n">
-        <v>0.9418153057212033</v>
+        <v>0.8612580967584362</v>
       </c>
       <c r="AA5" s="4" t="inlineStr">
-        <is>
-          <t>+/−/+</t>
-        </is>
-      </c>
-      <c r="AB5" s="6" t="n">
-        <v>0.8612580967584362</v>
-      </c>
-      <c r="AC5" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -19099,63 +19063,57 @@
         <v>5.851987306617745</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>1.903778390449249</v>
-      </c>
-      <c r="K6" s="3" t="n">
         <v>78.60895386021014</v>
       </c>
+      <c r="K6" s="6" t="n">
+        <v>0.5970948482796824</v>
+      </c>
       <c r="L6" s="6" t="n">
-        <v>0.5970948482796824</v>
-      </c>
-      <c r="M6" s="6" t="n">
         <v>0.4755954945528405</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>367.4853176721837</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>12.6068541079242</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>28.55589482658624</v>
-      </c>
-      <c r="P6" s="3" t="n">
         <v>7.925373974714658</v>
       </c>
+      <c r="P6" s="6" t="n">
+        <v>0.5089577419511414</v>
+      </c>
       <c r="Q6" s="3" t="n">
-        <v>45.42372399694379</v>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v>0.5089577419511414</v>
-      </c>
+        <v>1.218787898205369</v>
+      </c>
+      <c r="R6" s="4" t="inlineStr"/>
       <c r="S6" s="3" t="n">
-        <v>1.218787898205369</v>
-      </c>
-      <c r="T6" s="4" t="inlineStr"/>
+        <v>-21.12027409499712</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>-2716.50884098965</v>
+      </c>
       <c r="U6" s="3" t="n">
-        <v>-21.12027409499712</v>
-      </c>
-      <c r="V6" s="3" t="n">
-        <v>-2716.50884098965</v>
+        <v>-12.2498747285786</v>
+      </c>
+      <c r="V6" s="6" t="n">
+        <v>-0.4869274011206267</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>-12.2498747285786</v>
-      </c>
-      <c r="X6" s="6" t="n">
-        <v>-0.4869274011206267</v>
-      </c>
-      <c r="Y6" s="3" t="n">
         <v>-758000000</v>
       </c>
-      <c r="Z6" s="3" t="n">
+      <c r="X6" s="3" t="n">
         <v>1.035065537957942</v>
       </c>
+      <c r="Y6" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
+      </c>
+      <c r="Z6" s="6" t="n">
+        <v>0.1934566440136914</v>
+      </c>
       <c r="AA6" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB6" s="6" t="n">
-        <v>0.1934566440136914</v>
-      </c>
-      <c r="AC6" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -19192,63 +19150,57 @@
         <v>5.670483584067544</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1.462203203717169</v>
-      </c>
-      <c r="K7" s="3" t="n">
         <v>75.86497626779915</v>
       </c>
+      <c r="K7" s="6" t="n">
+        <v>0.7751004016064257</v>
+      </c>
       <c r="L7" s="6" t="n">
-        <v>0.7751004016064257</v>
-      </c>
-      <c r="M7" s="6" t="n">
         <v>0.62856689917565</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>314.3356190969077</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>20.03345827414021</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>17.96993784466554</v>
-      </c>
-      <c r="P7" s="3" t="n">
         <v>8.426600816835895</v>
       </c>
+      <c r="P7" s="6" t="n">
+        <v>0.5735922915587045</v>
+      </c>
       <c r="Q7" s="3" t="n">
-        <v>42.72185283545642</v>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v>0.5735922915587045</v>
-      </c>
+        <v>1.372064584494235</v>
+      </c>
+      <c r="R7" s="4" t="inlineStr"/>
       <c r="S7" s="3" t="n">
-        <v>1.372064584494235</v>
-      </c>
-      <c r="T7" s="4" t="inlineStr"/>
+        <v>16.8882992482486</v>
+      </c>
+      <c r="T7" s="3" t="n">
+        <v>-17.74082345331284</v>
+      </c>
       <c r="U7" s="3" t="n">
-        <v>16.8882992482486</v>
-      </c>
-      <c r="V7" s="3" t="n">
-        <v>-17.74082345331284</v>
+        <v>21.91259326937719</v>
+      </c>
+      <c r="V7" s="6" t="n">
+        <v>0.3751676673196782</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>21.91259326937719</v>
-      </c>
-      <c r="X7" s="6" t="n">
-        <v>0.3751676673196782</v>
-      </c>
-      <c r="Y7" s="3" t="n">
         <v>-3120000000</v>
       </c>
-      <c r="Z7" s="3" t="n">
+      <c r="X7" s="3" t="n">
         <v>1.082311614943673</v>
       </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>−/−/+</t>
+        </is>
+      </c>
+      <c r="Z7" s="6" t="n">
+        <v>0.2494202408671759</v>
+      </c>
       <c r="AA7" s="4" t="inlineStr">
-        <is>
-          <t>−/−/+</t>
-        </is>
-      </c>
-      <c r="AB7" s="6" t="n">
-        <v>0.2494202408671759</v>
-      </c>
-      <c r="AC7" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -19284,64 +19236,58 @@
       <c r="I8" s="3" t="n">
         <v>3.851814716877724</v>
       </c>
-      <c r="J8" s="6" t="n">
-        <v>0.5047658704854132</v>
-      </c>
-      <c r="K8" s="3" t="n">
+      <c r="J8" s="3" t="n">
         <v>79.16383268151674</v>
       </c>
+      <c r="K8" s="6" t="n">
+        <v>0.8343694905817945</v>
+      </c>
       <c r="L8" s="6" t="n">
-        <v>0.8343694905817945</v>
-      </c>
-      <c r="M8" s="6" t="n">
         <v>0.7108657325786397</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>379.973474801061</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>24.55363296509719</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>14.66178143624356</v>
-      </c>
-      <c r="P8" s="3" t="n">
         <v>11.60224392832397</v>
       </c>
+      <c r="P8" s="6" t="n">
+        <v>0.8626314292927965</v>
+      </c>
       <c r="Q8" s="3" t="n">
-        <v>31.02848054428076</v>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v>0.8626314292927965</v>
-      </c>
+        <v>1.637930851432139</v>
+      </c>
+      <c r="R8" s="4" t="inlineStr"/>
       <c r="S8" s="3" t="n">
-        <v>1.637930851432139</v>
-      </c>
-      <c r="T8" s="4" t="inlineStr"/>
+        <v>104.0026169030888</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>-98.43812535742727</v>
+      </c>
       <c r="U8" s="3" t="n">
-        <v>104.0026169030888</v>
-      </c>
-      <c r="V8" s="3" t="n">
-        <v>-98.43812535742727</v>
+        <v>46.91481388958281</v>
+      </c>
+      <c r="V8" s="6" t="n">
+        <v>0.2239224544515465</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>46.91481388958281</v>
-      </c>
-      <c r="X8" s="6" t="n">
-        <v>0.2239224544515465</v>
-      </c>
-      <c r="Y8" s="3" t="n">
         <v>-4536000000</v>
       </c>
-      <c r="Z8" s="3" t="n">
+      <c r="X8" s="3" t="n">
         <v>1.076763058321679</v>
       </c>
+      <c r="Y8" s="4" t="inlineStr">
+        <is>
+          <t>−/−/+</t>
+        </is>
+      </c>
+      <c r="Z8" s="6" t="n">
+        <v>0.26738983455943</v>
+      </c>
       <c r="AA8" s="4" t="inlineStr">
-        <is>
-          <t>−/−/+</t>
-        </is>
-      </c>
-      <c r="AB8" s="6" t="n">
-        <v>0.26738983455943</v>
-      </c>
-      <c r="AC8" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -19377,64 +19323,58 @@
       <c r="I9" s="3" t="n">
         <v>4.733211932825113</v>
       </c>
-      <c r="J9" s="6" t="n">
-        <v>-0.04411118995996729</v>
-      </c>
-      <c r="K9" s="3" t="n">
+      <c r="J9" s="3" t="n">
         <v>85.94984876573322</v>
       </c>
+      <c r="K9" s="6" t="n">
+        <v>0.6950447093889717</v>
+      </c>
       <c r="L9" s="6" t="n">
-        <v>0.6950447093889717</v>
-      </c>
-      <c r="M9" s="6" t="n">
         <v>0.6011283798169044</v>
+      </c>
+      <c r="M9" s="3" t="n">
+        <v>611.7361111111111</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>16.9585795442678</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>21.22819302526338</v>
-      </c>
-      <c r="P9" s="3" t="n">
         <v>11.11995318401223</v>
       </c>
+      <c r="P9" s="6" t="n">
+        <v>0.729288105293561</v>
+      </c>
       <c r="Q9" s="3" t="n">
-        <v>32.37423701725578</v>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v>0.729288105293561</v>
-      </c>
+        <v>1.350157567544121</v>
+      </c>
+      <c r="R9" s="4" t="inlineStr"/>
       <c r="S9" s="3" t="n">
-        <v>1.350157567544121</v>
-      </c>
-      <c r="T9" s="4" t="inlineStr"/>
+        <v>5.092983059398996</v>
+      </c>
+      <c r="T9" s="3" t="n">
+        <v>20.37791689464336</v>
+      </c>
       <c r="U9" s="3" t="n">
-        <v>5.092983059398996</v>
+        <v>8.920676755653817</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>20.37791689464336</v>
+        <v>-1.539195676743165</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>8.920676755653817</v>
+        <v>2933000000</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>-1.539195676743165</v>
-      </c>
-      <c r="Y9" s="3" t="n">
-        <v>2933000000</v>
-      </c>
-      <c r="Z9" s="3" t="n">
         <v>1.153843217875552</v>
       </c>
+      <c r="Y9" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
+      </c>
+      <c r="Z9" s="6" t="n">
+        <v>0.07606145932765151</v>
+      </c>
       <c r="AA9" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB9" s="6" t="n">
-        <v>0.07606145932765151</v>
-      </c>
-      <c r="AC9" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -19470,64 +19410,58 @@
       <c r="I10" s="3" t="n">
         <v>3.847406798434025</v>
       </c>
-      <c r="J10" s="6" t="n">
-        <v>-0.2028576001318476</v>
-      </c>
-      <c r="K10" s="3" t="n">
+      <c r="J10" s="3" t="n">
         <v>87.38290025857319</v>
       </c>
+      <c r="K10" s="6" t="n">
+        <v>0.8653773028256736</v>
+      </c>
       <c r="L10" s="6" t="n">
-        <v>0.8653773028256736</v>
-      </c>
-      <c r="M10" s="6" t="n">
         <v>0.831915033108241</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>692.5751721820931</v>
       </c>
       <c r="N10" s="3" t="n">
         <v>60.38927706064477</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>5.961323226944362</v>
+        <v>45.7556119419931</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>45.7556119419931</v>
+        <v>1.994050121267092</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>7.867887341478283</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>1.994050121267092</v>
-      </c>
+        <v>3.152056061527222</v>
+      </c>
+      <c r="R10" s="4" t="inlineStr"/>
       <c r="S10" s="3" t="n">
-        <v>3.152056061527222</v>
-      </c>
-      <c r="T10" s="4" t="inlineStr"/>
+        <v>305.0443410297746</v>
+      </c>
+      <c r="T10" s="3" t="n">
+        <v>214.0351159943363</v>
+      </c>
       <c r="U10" s="3" t="n">
-        <v>305.0443410297746</v>
+        <v>84.14284320421503</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>214.0351159943363</v>
+        <v>4.749883323976259</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>84.14284320421503</v>
+        <v>15371000000</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>4.749883323976259</v>
-      </c>
-      <c r="Y10" s="3" t="n">
-        <v>15371000000</v>
+        <v>1.102848929904304</v>
+      </c>
+      <c r="Y10" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>1.102848929904304</v>
+        <v>1.642744958431796</v>
       </c>
       <c r="AA10" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB10" s="3" t="n">
-        <v>1.642744958431796</v>
-      </c>
-      <c r="AC10" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>
@@ -19563,64 +19497,58 @@
       <c r="I11" s="3" t="n">
         <v>4.81923324957763</v>
       </c>
-      <c r="J11" s="6" t="n">
-        <v>-0.2543283386707769</v>
+      <c r="J11" s="3" t="n">
+        <v>70.91295706919794</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>70.91295706919794</v>
+        <v>1.054247598719317</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>1.054247598719317</v>
+        <v>1.028132337246531</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>1.028132337246531</v>
+        <v>243.7956901906446</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>80.55326336707175</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>4.469092684172487</v>
+        <v>63.15651078498099</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>63.15651078498099</v>
+        <v>1.385433639477316</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>5.700124904392442</v>
-      </c>
-      <c r="R11" s="3" t="n">
-        <v>1.385433639477316</v>
-      </c>
+        <v>2.003309078584667</v>
+      </c>
+      <c r="R11" s="4" t="inlineStr"/>
       <c r="S11" s="3" t="n">
-        <v>2.003309078584667</v>
-      </c>
-      <c r="T11" s="4" t="inlineStr"/>
+        <v>13.69223490807921</v>
+      </c>
+      <c r="T11" s="3" t="n">
+        <v>29.67486979398028</v>
+      </c>
       <c r="U11" s="3" t="n">
-        <v>13.69223490807921</v>
+        <v>52.50095375355009</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>29.67486979398028</v>
+        <v>4.703957037406879</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>52.50095375355009</v>
+        <v>24744000000</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>4.703957037406879</v>
-      </c>
-      <c r="Y11" s="3" t="n">
-        <v>24744000000</v>
+        <v>1.128348358704674</v>
+      </c>
+      <c r="Y11" s="4" t="inlineStr">
+        <is>
+          <t>+/−/+</t>
+        </is>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>1.128348358704674</v>
+        <v>1.627033100638936</v>
       </c>
       <c r="AA11" s="4" t="inlineStr">
-        <is>
-          <t>+/−/+</t>
-        </is>
-      </c>
-      <c r="AB11" s="3" t="n">
-        <v>1.627033100638936</v>
-      </c>
-      <c r="AC11" s="4" t="inlineStr">
         <is>
           <t>危险区</t>
         </is>

--- a/data/601127_赛力斯_财务数据.xlsx
+++ b/data/601127_赛力斯_财务数据.xlsx
@@ -39141,7 +39141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P40"/>
+  <dimension ref="A1:S40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39220,6 +39220,21 @@
           <t>净利润增长率</t>
         </is>
       </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>有息负债率</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>经营现金流/营收</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>权益乘数</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -39268,6 +39283,15 @@
       <c r="P2" t="n">
         <v>-0.7882532608192565</v>
       </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.0585748880967059</v>
+      </c>
+      <c r="S2" t="n">
+        <v>5.16353591160221</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -39320,6 +39344,15 @@
       <c r="P3" t="n">
         <v>0.6100272339242017</v>
       </c>
+      <c r="Q3" t="n">
+        <v>0.1401869158878505</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.09691336177580845</v>
+      </c>
+      <c r="S3" t="n">
+        <v>4.294516676088185</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -39372,6 +39405,15 @@
       <c r="P4" t="n">
         <v>0.4720045937374342</v>
       </c>
+      <c r="Q4" t="n">
+        <v>0.128184250319879</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.08439984324308385</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4.732727773190201</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -39424,6 +39466,15 @@
       <c r="P5" t="n">
         <v>2.455630052819517</v>
       </c>
+      <c r="Q5" t="n">
+        <v>0.2091169773129797</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.04545503471337813</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5.019898391193903</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -39476,6 +39527,15 @@
       <c r="P6" t="n">
         <v>-0.7397401969098364</v>
       </c>
+      <c r="Q6" t="n">
+        <v>0.1314066516664323</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.0886898865503485</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5.263508512213176</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -39528,6 +39588,15 @@
       <c r="P7" t="n">
         <v>0.8456486357185928</v>
       </c>
+      <c r="Q7" t="n">
+        <v>0.1713964734039955</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.03624302593937281</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5.151736285858077</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -39580,6 +39649,15 @@
       <c r="P8" t="n">
         <v>0.2906269031137751</v>
       </c>
+      <c r="Q8" t="n">
+        <v>0.1675079287086255</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.01764290110637343</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5.493742331288344</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -39632,6 +39710,15 @@
       <c r="P9" t="n">
         <v>-0.272213909876411</v>
       </c>
+      <c r="Q9" t="n">
+        <v>0.2043382818022845</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.05518833809613006</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5.087450312322544</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -39684,6 +39771,15 @@
       <c r="P10" t="n">
         <v>-0.1940912757762256</v>
       </c>
+      <c r="Q10" t="n">
+        <v>0.2067165064673075</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.1048447219517924</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5.138414634146342</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -39736,6 +39832,15 @@
       <c r="P11" t="n">
         <v>0.2396204178392056</v>
       </c>
+      <c r="Q11" t="n">
+        <v>0.2144827042786226</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.07920895503333507</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5.315602094240838</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -39788,6 +39893,15 @@
       <c r="P12" t="n">
         <v>-0.328296819456443</v>
       </c>
+      <c r="Q12" t="n">
+        <v>0.2099948110006786</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.03997861605102725</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4.996609493418428</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -39840,6 +39954,15 @@
       <c r="P13" t="n">
         <v>-0.7439028281067208</v>
       </c>
+      <c r="Q13" t="n">
+        <v>0.1853014865542008</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.01831016463661296</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5.400505141620061</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -39892,6 +40015,15 @@
       <c r="P14" t="n">
         <v>-1.637946084329863</v>
       </c>
+      <c r="Q14" t="n">
+        <v>0.2061418853255588</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-0.06441971010626478</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4.973897911832947</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -39944,6 +40076,15 @@
       <c r="P15" t="n">
         <v>3.898648822267324</v>
       </c>
+      <c r="Q15" t="n">
+        <v>0.2169490183660545</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.01821921755392196</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5.106933495047503</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -39996,6 +40137,15 @@
       <c r="P16" t="n">
         <v>0.6500281272534356</v>
       </c>
+      <c r="Q16" t="n">
+        <v>0.2162996975328887</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.01341465532877671</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5.288302177683561</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -40048,6 +40198,15 @@
       <c r="P17" t="n">
         <v>4.074234997536863</v>
       </c>
+      <c r="Q17" t="n">
+        <v>0.1958276229633014</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.0760707447512997</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5.087739686228937</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -40100,6 +40259,15 @@
       <c r="P18" t="n">
         <v>-0.7042940081514657</v>
       </c>
+      <c r="Q18" t="n">
+        <v>0.2106233062330623</v>
+      </c>
+      <c r="R18" t="n">
+        <v>-0.2008351929954397</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5.473694620253164</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -40152,6 +40320,15 @@
       <c r="P19" t="n">
         <v>0.05985322191704112</v>
       </c>
+      <c r="Q19" t="n">
+        <v>0.203685530476502</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.05088072093158025</v>
+      </c>
+      <c r="S19" t="n">
+        <v>4.23733251193593</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -40204,6 +40381,15 @@
       <c r="P20" t="n">
         <v>0.4974339508740804</v>
       </c>
+      <c r="Q20" t="n">
+        <v>0.2141743941401075</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.0501894936354295</v>
+      </c>
+      <c r="S20" t="n">
+        <v>4.254973474801061</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -40256,6 +40442,15 @@
       <c r="P21" t="n">
         <v>1.50884334461539</v>
       </c>
+      <c r="Q21" t="n">
+        <v>0.1465151136647514</v>
+      </c>
+      <c r="R21" t="n">
+        <v>-0.0590384416905828</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4.023115577889448</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -40308,6 +40503,15 @@
       <c r="P22" t="n">
         <v>-0.7705147679961155</v>
       </c>
+      <c r="Q22" t="n">
+        <v>0.2025688948979998</v>
+      </c>
+      <c r="R22" t="n">
+        <v>-0.07936586613431244</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5.242234730039608</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -40360,6 +40564,15 @@
       <c r="P23" t="n">
         <v>0.1758486721559402</v>
       </c>
+      <c r="Q23" t="n">
+        <v>0.164840970730161</v>
+      </c>
+      <c r="R23" t="n">
+        <v>-0.02220870056643743</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.641739353514623</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -40412,6 +40625,15 @@
       <c r="P24" t="n">
         <v>1.211251933601696</v>
       </c>
+      <c r="Q24" t="n">
+        <v>0.1766891426998762</v>
+      </c>
+      <c r="R24" t="n">
+        <v>-0.06899789058531136</v>
+      </c>
+      <c r="S24" t="n">
+        <v>4.011592602815347</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -40464,6 +40686,15 @@
       <c r="P25" t="n">
         <v>2.325681956023442</v>
       </c>
+      <c r="Q25" t="n">
+        <v>0.09458425437850705</v>
+      </c>
+      <c r="R25" t="n">
+        <v>-0.03427650287770723</v>
+      </c>
+      <c r="S25" t="n">
+        <v>4.119789842381786</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -40516,6 +40747,15 @@
       <c r="P26" t="n">
         <v>-0.7847014340349491</v>
       </c>
+      <c r="Q26" t="n">
+        <v>0.1459890977331625</v>
+      </c>
+      <c r="R26" t="n">
+        <v>-0.03001246755587406</v>
+      </c>
+      <c r="S26" t="n">
+        <v>4.701162302198572</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -40568,6 +40808,15 @@
       <c r="P27" t="n">
         <v>1.060856102321422</v>
       </c>
+      <c r="Q27" t="n">
+        <v>0.1318042515931313</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.02537059888899964</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.07647410954804</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -40620,6 +40869,15 @@
       <c r="P28" t="n">
         <v>0.5464389983221463</v>
       </c>
+      <c r="Q28" t="n">
+        <v>0.09590696613841067</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.05176599249498593</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.522207051642438</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -40672,6 +40930,15 @@
       <c r="P29" t="n">
         <v>0.1604112661952595</v>
       </c>
+      <c r="Q29" t="n">
+        <v>0.06451361108400819</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.1785058735846741</v>
+      </c>
+      <c r="S29" t="n">
+        <v>4.492810801332633</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -40724,6 +40991,15 @@
       <c r="P30" t="n">
         <v>-0.7859061095230813</v>
       </c>
+      <c r="Q30" t="n">
+        <v>0.1457498085499347</v>
+      </c>
+      <c r="R30" t="n">
+        <v>-0.4258828984618748</v>
+      </c>
+      <c r="S30" t="n">
+        <v>4.112830013895322</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -40776,6 +41052,15 @@
       <c r="P31" t="n">
         <v>1.404122893240687</v>
       </c>
+      <c r="Q31" t="n">
+        <v>0.1606911447084233</v>
+      </c>
+      <c r="R31" t="n">
+        <v>-0.2760066277601506</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.615775087856306</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -40828,6 +41113,15 @@
       <c r="P32" t="n">
         <v>0.6129299465246443</v>
       </c>
+      <c r="Q32" t="n">
+        <v>0.1449293900941465</v>
+      </c>
+      <c r="R32" t="n">
+        <v>-0.05155836724426571</v>
+      </c>
+      <c r="S32" t="n">
+        <v>4.21433962264151</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -40880,6 +41174,15 @@
       <c r="P33" t="n">
         <v>-2.373605955542587</v>
       </c>
+      <c r="Q33" t="n">
+        <v>0.01532364037132805</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0.1550878078834493</v>
+      </c>
+      <c r="S33" t="n">
+        <v>7.694390084801044</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -40932,6 +41235,15 @@
       <c r="P34" t="n">
         <v>-0.981232169200324</v>
       </c>
+      <c r="Q34" t="n">
+        <v>0.0457384422230345</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0.04469012508378374</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5.410404127257094</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -40984,6 +41296,15 @@
       <c r="P35" t="n">
         <v>14.2775984076795</v>
       </c>
+      <c r="Q35" t="n">
+        <v>0.03001807879442348</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0.2515202368425056</v>
+      </c>
+      <c r="S35" t="n">
+        <v>6.224378823351711</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -41036,6 +41357,15 @@
       <c r="P36" t="n">
         <v>1.508778370493713</v>
       </c>
+      <c r="Q36" t="n">
+        <v>0.02137909939041709</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.1876831525546214</v>
+      </c>
+      <c r="S36" t="n">
+        <v>6.785618977020015</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -41088,6 +41418,15 @@
       <c r="P37" t="n">
         <v>0.8027037186263135</v>
       </c>
+      <c r="Q37" t="n">
+        <v>0.03458507636929663</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.1751794179683359</v>
+      </c>
+      <c r="S37" t="n">
+        <v>3.516936311647686</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -41140,6 +41479,15 @@
       <c r="P38" t="n">
         <v>-0.8795084312442087</v>
       </c>
+      <c r="Q38" t="n">
+        <v>0.08467227231283558</v>
+      </c>
+      <c r="R38" t="n">
+        <v>-0.3984941745245644</v>
+      </c>
+      <c r="S38" t="n">
+        <v>4.268355962985384</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -41192,6 +41540,15 @@
       <c r="P39" t="n">
         <v>3.155060070545563</v>
       </c>
+      <c r="Q39" t="n">
+        <v>0.052580770865807</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0.2313557919398868</v>
+      </c>
+      <c r="S39" t="n">
+        <v>4.219274317103247</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -41243,6 +41600,15 @@
       </c>
       <c r="P40" t="n">
         <v>0.8317485072975508</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0.04188270538080424</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0.2049044980188411</v>
+      </c>
+      <c r="S40" t="n">
+        <v>4.370247814983995</v>
       </c>
     </row>
   </sheetData>
